--- a/TestData/T1644_FEISFormSubmitforReview.xlsx
+++ b/TestData/T1644_FEISFormSubmitforReview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20380"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EEB979-704A-4897-8A46-4C3F3A04D2AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF17586-B108-4848-980A-8C6A17F3F518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13170" windowHeight="5550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -347,11 +347,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -656,202 +654,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="3"/>
-    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="3"/>
-    <col min="15" max="17" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.85546875" style="3"/>
-    <col min="26" max="26" width="11.28515625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="8.85546875" style="3"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>83</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" t="s">
         <v>18</v>
       </c>
       <c r="N2" t="s">
         <v>87</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" t="s">
         <v>30</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" t="s">
         <v>59</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AA2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AB2" s="3" t="s">
         <v>39</v>
       </c>
     </row>
@@ -864,13 +858,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -878,7 +872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -894,17 +888,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -930,7 +924,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -965,253 +959,253 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="95.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.85546875" style="10"/>
-    <col min="17" max="17" width="10.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="10" customWidth="1"/>
-    <col min="19" max="19" width="12.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.85546875" style="10"/>
-    <col min="21" max="21" width="102.28515625" style="10" customWidth="1"/>
-    <col min="22" max="16384" width="8.85546875" style="10"/>
+    <col min="1" max="1" width="95.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.88671875" style="8"/>
+    <col min="17" max="17" width="10.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="8" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" style="8"/>
+    <col min="21" max="21" width="102.33203125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:21" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="T1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="120.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:21" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="9" t="s">
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-    </row>
-    <row r="16" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-    </row>
-    <row r="17" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-    </row>
-    <row r="18" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-    </row>
-    <row r="19" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-    </row>
-    <row r="20" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-    </row>
-    <row r="21" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-    </row>
-    <row r="22" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-    </row>
-    <row r="23" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-    </row>
-    <row r="24" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-    </row>
-    <row r="25" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-    </row>
-    <row r="26" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-    </row>
-    <row r="27" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-    </row>
-    <row r="28" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-    </row>
-    <row r="29" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-    </row>
-    <row r="30" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-    </row>
-    <row r="31" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-    </row>
-    <row r="32" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-    </row>
-    <row r="33" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+    </row>
+    <row r="16" spans="1:21" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+    </row>
+    <row r="18" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+    </row>
+    <row r="22" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+    </row>
+    <row r="26" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+    </row>
+    <row r="27" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+    </row>
+    <row r="29" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="31" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+    </row>
+    <row r="32" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+    </row>
+    <row r="33" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
